--- a/MC.PA.xlsx
+++ b/MC.PA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B972BBC5-508F-49F7-A698-6DD9901069B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470C30D9-A962-4C10-B48A-CA8E267EB484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="2" xr2:uid="{833B3248-1BC2-4BAF-AC24-6FD47873AD76}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{833B3248-1BC2-4BAF-AC24-6FD47873AD76}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -46,6 +46,7 @@
     <author>tc={04D8DA85-74C1-43F7-9161-C9F4B5E4FC35}</author>
     <author>tc={F8C88AB7-0E52-4349-A875-E61A1AD7BCCB}</author>
     <author>tc={6A0FBB0C-E2C5-451B-89D8-64036F47AC91}</author>
+    <author>tc={6035DA54-C778-4C24-ADB7-572487D25008}</author>
   </authors>
   <commentList>
     <comment ref="G6" authorId="0" shapeId="0" xr:uid="{0730EDA6-8BD7-4887-A459-F5F3D684BDDA}">
@@ -78,6 +79,14 @@
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Organic Growth +1%</t>
+      </text>
+    </comment>
+    <comment ref="K28" authorId="4" shapeId="0" xr:uid="{6035DA54-C778-4C24-ADB7-572487D25008}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Organic Growth (- impact fx) +1%</t>
       </text>
     </comment>
   </commentList>
@@ -141,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="276">
   <si>
     <t>LVMH</t>
   </si>
@@ -958,6 +967,18 @@
   <si>
     <t>Increased stake in Loro Piana Q425</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -974,13 +995,19 @@
     <numFmt numFmtId="171" formatCode="0.0"/>
     <numFmt numFmtId="172" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1307,143 +1334,147 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="13" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="7" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="8" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1993,6 +2024,9 @@
   <threadedComment ref="I28" dT="2025-10-18T12:40:47.40" personId="{2567B180-7FBF-4C5E-A839-9F212724FCA9}" id="{6A0FBB0C-E2C5-451B-89D8-64036F47AC91}">
     <text>Organic Growth +1%</text>
   </threadedComment>
+  <threadedComment ref="K28" dT="2026-04-17T15:31:16.55" personId="{2567B180-7FBF-4C5E-A839-9F212724FCA9}" id="{6035DA54-C778-4C24-ADB7-572487D25008}">
+    <text>Organic Growth (- impact fx) +1%</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -2030,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="43">
-        <v>549</v>
+        <v>499.3</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2043,8 +2077,8 @@
       <c r="I5" s="43">
         <v>497.68693999999999</v>
       </c>
-      <c r="J5" s="77" t="s">
-        <v>225</v>
+      <c r="J5" s="85" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -2053,7 +2087,7 @@
       </c>
       <c r="I6" s="61">
         <f>I5*I4</f>
-        <v>273230.13006</v>
+        <v>248495.08914200001</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -2076,8 +2110,8 @@
       <c r="I7" s="61">
         <v>8794</v>
       </c>
-      <c r="J7" s="77" t="s">
-        <v>225</v>
+      <c r="J7" s="85" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2098,8 +2132,8 @@
         <f>12418+7925</f>
         <v>20343</v>
       </c>
-      <c r="J8" s="77" t="s">
-        <v>225</v>
+      <c r="J8" s="85" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -2121,7 +2155,7 @@
       </c>
       <c r="I9" s="61">
         <f>I6+I8-I7</f>
-        <v>284779.13006</v>
+        <v>260044.08914200001</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -2352,6 +2386,18 @@
       <c r="J2" s="57" t="s">
         <v>225</v>
       </c>
+      <c r="K2" s="85" t="s">
+        <v>272</v>
+      </c>
+      <c r="L2" s="85" t="s">
+        <v>273</v>
+      </c>
+      <c r="M2" s="85" t="s">
+        <v>274</v>
+      </c>
+      <c r="N2" s="85" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B3" s="4" t="s">
@@ -2502,8 +2548,13 @@
       <c r="I9" s="21">
         <v>1330</v>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
+      <c r="J9" s="21">
+        <f>+Model!Q13-SUM(Quarters!G9:I9)</f>
+        <v>1440</v>
+      </c>
+      <c r="K9" s="21">
+        <v>1273</v>
+      </c>
       <c r="L9" s="21"/>
       <c r="M9" s="43"/>
       <c r="N9" s="43"/>
@@ -2559,8 +2610,13 @@
       <c r="I10" s="21">
         <v>8497</v>
       </c>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
+      <c r="J10" s="21">
+        <f>+Model!Q14-SUM(Quarters!G10:I10)</f>
+        <v>10159</v>
+      </c>
+      <c r="K10" s="21">
+        <v>9247</v>
+      </c>
       <c r="L10" s="21"/>
       <c r="M10" s="43"/>
       <c r="N10" s="43"/>
@@ -2616,8 +2672,13 @@
       <c r="I11" s="21">
         <v>1958</v>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
+      <c r="J11" s="21">
+        <f>+Model!Q15-SUM(Quarters!G11:I11)</f>
+        <v>2134</v>
+      </c>
+      <c r="K11" s="21">
+        <v>2038</v>
+      </c>
       <c r="L11" s="21"/>
       <c r="M11" s="43"/>
       <c r="N11" s="43"/>
@@ -2673,8 +2734,13 @@
       <c r="I12" s="21">
         <v>2319</v>
       </c>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
+      <c r="J12" s="21">
+        <f>+Model!Q16-SUM(Quarters!G12:I12)</f>
+        <v>3077</v>
+      </c>
+      <c r="K12" s="21">
+        <v>2443</v>
+      </c>
       <c r="L12" s="21"/>
       <c r="M12" s="43"/>
       <c r="N12" s="43"/>
@@ -2730,8 +2796,13 @@
       <c r="I13" s="21">
         <v>3992</v>
       </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
+      <c r="J13" s="21">
+        <f>+Model!Q17-SUM(Quarters!G13:I13)</f>
+        <v>5736</v>
+      </c>
+      <c r="K13" s="21">
+        <v>4048</v>
+      </c>
       <c r="L13" s="21"/>
       <c r="M13" s="43"/>
       <c r="N13" s="43"/>
@@ -2789,8 +2860,13 @@
       <c r="I14" s="21">
         <v>185</v>
       </c>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
+      <c r="J14" s="21">
+        <f>+Model!Q18-SUM(Quarters!G14:I14)</f>
+        <v>169</v>
+      </c>
+      <c r="K14" s="21">
+        <v>72</v>
+      </c>
       <c r="L14" s="21"/>
       <c r="M14" s="43"/>
       <c r="N14" s="43"/>
@@ -2852,8 +2928,13 @@
         <f>+SUM(I9:I14)</f>
         <v>18281</v>
       </c>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
+      <c r="J15" s="64">
+        <f>+Model!Q19-SUM(Quarters!G15:I15)</f>
+        <v>22715</v>
+      </c>
+      <c r="K15" s="86">
+        <v>19121</v>
+      </c>
       <c r="L15" s="43"/>
       <c r="M15" s="43"/>
       <c r="N15" s="43"/>
@@ -2945,10 +3026,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="J17" s="68" t="e">
-        <f t="shared" ref="J17:J22" si="2">+J3/F3-1</f>
+        <f t="shared" ref="J17:K22" si="2">+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K17" s="43"/>
+      <c r="K17" s="68">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
       <c r="L17" s="43"/>
       <c r="M17" s="43"/>
       <c r="N17" s="43"/>
@@ -3004,7 +3088,10 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K18" s="43"/>
+      <c r="K18" s="68">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
       <c r="L18" s="43"/>
       <c r="M18" s="43"/>
       <c r="N18" s="43"/>
@@ -3059,7 +3146,10 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K19" s="43"/>
+      <c r="K19" s="68">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
       <c r="L19" s="43"/>
       <c r="M19" s="43"/>
       <c r="N19" s="43"/>
@@ -3114,7 +3204,10 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K20" s="43"/>
+      <c r="K20" s="68">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
       <c r="L20" s="43"/>
       <c r="M20" s="43"/>
       <c r="N20" s="43"/>
@@ -3169,7 +3262,10 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K21" s="43"/>
+      <c r="K21" s="68">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
       <c r="L21" s="43"/>
       <c r="M21" s="43"/>
       <c r="N21" s="43"/>
@@ -3224,7 +3320,10 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K22" s="43"/>
+      <c r="K22" s="68">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
       <c r="L22" s="43"/>
       <c r="M22" s="43"/>
       <c r="N22" s="43"/>
@@ -3268,7 +3367,7 @@
         <v>-7.9040225829216659E-2</v>
       </c>
       <c r="H23" s="68">
-        <f t="shared" ref="H23:J27" si="3">+H9/D9-1</f>
+        <f t="shared" ref="H23:K27" si="3">+H9/D9-1</f>
         <v>-7.7641984184040225E-2</v>
       </c>
       <c r="I23" s="68">
@@ -3279,7 +3378,10 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K23" s="43"/>
+      <c r="K23" s="68">
+        <f t="shared" si="3"/>
+        <v>-2.4521072796934829E-2</v>
+      </c>
       <c r="L23" s="43"/>
       <c r="M23" s="43"/>
       <c r="N23" s="43"/>
@@ -3334,7 +3436,10 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K24" s="43"/>
+      <c r="K24" s="68">
+        <f t="shared" si="3"/>
+        <v>-8.5180055401662069E-2</v>
+      </c>
       <c r="L24" s="43"/>
       <c r="M24" s="43"/>
       <c r="N24" s="43"/>
@@ -3389,7 +3494,10 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K25" s="43"/>
+      <c r="K25" s="68">
+        <f t="shared" si="3"/>
+        <v>-6.4279155188246118E-2</v>
+      </c>
       <c r="L25" s="43"/>
       <c r="M25" s="43"/>
       <c r="N25" s="43"/>
@@ -3444,7 +3552,10 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="43"/>
+      <c r="K26" s="68">
+        <f t="shared" si="3"/>
+        <v>-1.5713134568896003E-2</v>
+      </c>
       <c r="L26" s="43"/>
       <c r="M26" s="43"/>
       <c r="N26" s="43"/>
@@ -3499,7 +3610,10 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K27" s="43"/>
+      <c r="K27" s="68">
+        <f t="shared" si="3"/>
+        <v>-3.3659584626402506E-2</v>
+      </c>
       <c r="L27" s="43"/>
       <c r="M27" s="43"/>
       <c r="N27" s="43"/>
@@ -3543,7 +3657,7 @@
         <v>-1.85077800328598E-2</v>
       </c>
       <c r="H28" s="76">
-        <f t="shared" ref="H28:J28" si="5">+H15/D15-1</f>
+        <f t="shared" ref="H28:K28" si="5">+H15/D15-1</f>
         <v>-7.0676261735690749E-2</v>
       </c>
       <c r="I28" s="76">
@@ -3554,7 +3668,10 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K28" s="43"/>
+      <c r="K28" s="76">
+        <f t="shared" si="5"/>
+        <v>-5.8588941952636531E-2</v>
+      </c>
       <c r="L28" s="43"/>
       <c r="M28" s="43"/>
       <c r="N28" s="43"/>
@@ -29998,7 +30115,7 @@
       </c>
       <c r="J36" s="42">
         <f>Main!I6/Model!P34</f>
-        <v>21.77132510438247</v>
+        <v>19.800405509322712</v>
       </c>
       <c r="K36" s="42">
         <f>Main!J6/Model!Q34</f>
@@ -30037,7 +30154,7 @@
       </c>
       <c r="J37" s="42">
         <f>J36/-2</f>
-        <v>-10.885662552191235</v>
+        <v>-9.9002027546613558</v>
       </c>
       <c r="K37" s="42">
         <f>K36/-2</f>
@@ -30278,14 +30395,14 @@
       </c>
       <c r="J3" s="6">
         <f>+Main!I4</f>
-        <v>549</v>
+        <v>499.3</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>156</v>
       </c>
       <c r="O3" s="6">
         <f>+J3</f>
-        <v>549</v>
+        <v>499.3</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.2">
@@ -30294,14 +30411,14 @@
       </c>
       <c r="E4" s="7">
         <f ca="1">+TODAY()</f>
-        <v>46065</v>
+        <v>46129</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>158</v>
       </c>
       <c r="J4" s="8">
         <f ca="1">V62</f>
-        <v>472.81952388440197</v>
+        <v>470.18744702254469</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>159</v>
@@ -30323,7 +30440,7 @@
       </c>
       <c r="J5" s="11">
         <f ca="1">J4/J3-1</f>
-        <v>-0.13876225157668132</v>
+        <v>-5.830673538444886E-2</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>161</v>
@@ -31921,43 +32038,43 @@
       <c r="L52" s="40"/>
       <c r="M52" s="40">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>1641.7052536991489</v>
+        <v>4117.8650809753517</v>
       </c>
       <c r="N52" s="40">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>13851.641718484387</v>
+        <v>13637.780229757209</v>
       </c>
       <c r="O52" s="40">
         <f t="shared" ref="O52:U52" ca="1" si="20">O51/(1+$E$18)^O53</f>
-        <v>14230.007803776791</v>
+        <v>14010.3045573772</v>
       </c>
       <c r="P52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>14562.132003371178</v>
+        <v>14337.300947776755</v>
       </c>
       <c r="Q52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>14919.16171792587</v>
+        <v>14688.818326116987</v>
       </c>
       <c r="R52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>15229.092356476986</v>
+        <v>14993.963811463174</v>
       </c>
       <c r="S52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>14339.335193209801</v>
+        <v>14117.943993949606</v>
       </c>
       <c r="T52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>13132.460344366486</v>
+        <v>12929.702607992975</v>
       </c>
       <c r="U52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>12018.339682693913</v>
+        <v>11832.783337185789</v>
       </c>
       <c r="V52" s="41">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>10990.140327795592</v>
+        <v>10820.458796927922</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -31966,43 +32083,43 @@
       </c>
       <c r="M53" s="42">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.11666666666666667</v>
+        <v>0.29722222222222222</v>
       </c>
       <c r="N53" s="42">
         <f ca="1">M53+1</f>
-        <v>1.1166666666666667</v>
+        <v>1.2972222222222223</v>
       </c>
       <c r="O53" s="42">
         <f ca="1">N53+1</f>
-        <v>2.1166666666666667</v>
+        <v>2.2972222222222225</v>
       </c>
       <c r="P53" s="42">
         <f t="shared" ref="P53:V53" ca="1" si="21">O53+1</f>
-        <v>3.1166666666666667</v>
+        <v>3.2972222222222225</v>
       </c>
       <c r="Q53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>4.1166666666666671</v>
+        <v>4.2972222222222225</v>
       </c>
       <c r="R53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>5.1166666666666671</v>
+        <v>5.2972222222222225</v>
       </c>
       <c r="S53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>6.1166666666666671</v>
+        <v>6.2972222222222225</v>
       </c>
       <c r="T53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>7.1166666666666671</v>
+        <v>7.2972222222222225</v>
       </c>
       <c r="U53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>8.1166666666666671</v>
+        <v>8.2972222222222225</v>
       </c>
       <c r="V53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>9.1166666666666671</v>
+        <v>9.2972222222222225</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -32015,7 +32132,7 @@
       <c r="Q54" s="43"/>
       <c r="V54" s="21">
         <f ca="1">SUM(M52:V52)</f>
-        <v>124914.01640180015</v>
+        <v>125486.92168952296</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -32059,7 +32176,7 @@
       <c r="U56" s="45"/>
       <c r="V56" s="46">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>121951.08561248476</v>
+        <v>120068.23004553939</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -32087,7 +32204,7 @@
       <c r="U57" s="48"/>
       <c r="V57" s="49">
         <f ca="1">V54+V56</f>
-        <v>246865.10201428493</v>
+        <v>245555.15173506236</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -32141,7 +32258,7 @@
       <c r="Q60" s="43"/>
       <c r="V60" s="50">
         <f ca="1">V57+V58-V59</f>
-        <v>235316.10201428493</v>
+        <v>234006.15173506236</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -32178,7 +32295,7 @@
       </c>
       <c r="V62" s="50">
         <f ca="1">V60/V61</f>
-        <v>472.81952388440197</v>
+        <v>470.18744702254469</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
@@ -32239,7 +32356,7 @@
       </c>
       <c r="C69" s="52">
         <f ca="1">+J4</f>
-        <v>472.81952388440197</v>
+        <v>470.18744702254469</v>
       </c>
       <c r="D69" s="53">
         <v>0.01</v>
@@ -32267,7 +32384,7 @@
       </c>
       <c r="N69" s="52">
         <f ca="1">+J4</f>
-        <v>472.81952388440197</v>
+        <v>470.18744702254469</v>
       </c>
       <c r="O69" s="53">
         <v>0.08</v>
@@ -32298,25 +32415,25 @@
       </c>
       <c r="D70" s="55">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>751.90313992948563</v>
+        <v>748.85927750064809</v>
       </c>
       <c r="E70" s="55">
-        <v>781.49037087539295</v>
+        <v>778.13685957382859</v>
       </c>
       <c r="F70" s="55">
-        <v>818.17318209339589</v>
+        <v>814.43576223469506</v>
       </c>
       <c r="G70" s="56">
-        <v>864.99253655724931</v>
+        <v>860.76512287796993</v>
       </c>
       <c r="H70" s="55">
-        <v>927.01670588987872</v>
+        <v>922.14017049485699</v>
       </c>
       <c r="I70" s="55">
-        <v>1013.3685790125497</v>
+        <v>1007.5883172695244</v>
       </c>
       <c r="J70" s="55">
-        <v>1142.2939337677935</v>
+        <v>1135.1643875703071</v>
       </c>
       <c r="M70" s="83"/>
       <c r="N70" s="54">
@@ -32324,25 +32441,25 @@
       </c>
       <c r="O70" s="55">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>772.08538004304</v>
+        <v>768.83029785147153</v>
       </c>
       <c r="P70" s="55">
-        <v>790.86189198948136</v>
+        <v>787.41030185945147</v>
       </c>
       <c r="Q70" s="55">
-        <v>805.88310154663441</v>
+        <v>802.27430506583562</v>
       </c>
       <c r="R70" s="56">
-        <v>818.17318209339589</v>
+        <v>814.43576223469506</v>
       </c>
       <c r="S70" s="55">
-        <v>828.41491588236386</v>
+        <v>824.57030987541134</v>
       </c>
       <c r="T70" s="55">
-        <v>837.08099831918298</v>
+        <v>833.14569634063309</v>
       </c>
       <c r="U70" s="55">
-        <v>844.50906897931361</v>
+        <v>840.49602759653726</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
@@ -32351,50 +32468,50 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="55">
-        <v>624.19378532466339</v>
+        <v>621.38718260457085</v>
       </c>
       <c r="E71" s="55">
-        <v>639.64506931074504</v>
+        <v>636.65085971663677</v>
       </c>
       <c r="F71" s="55">
-        <v>657.96539865302771</v>
+        <v>654.7487467219629</v>
       </c>
       <c r="G71" s="56">
-        <v>680.11112180357804</v>
+        <v>676.6255802516356</v>
       </c>
       <c r="H71" s="55">
-        <v>707.51676144049645</v>
+        <v>703.69846525228479</v>
       </c>
       <c r="I71" s="55">
-        <v>742.43656748651256</v>
+        <v>738.19428092575811</v>
       </c>
       <c r="J71" s="55">
-        <v>788.62762314617487</v>
+        <v>783.82449260846681</v>
       </c>
       <c r="M71" s="83"/>
       <c r="N71" s="54">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="55">
-        <v>624.12004817765842</v>
+        <v>621.3143407615197</v>
       </c>
       <c r="P71" s="55">
-        <v>637.90889466762371</v>
+        <v>634.93576541207062</v>
       </c>
       <c r="Q71" s="55">
-        <v>648.93997185959597</v>
+        <v>645.83290513251143</v>
       </c>
       <c r="R71" s="56">
-        <v>657.96539865302771</v>
+        <v>654.7487467219629</v>
       </c>
       <c r="S71" s="55">
-        <v>665.4865876475543</v>
+        <v>662.17861471317246</v>
       </c>
       <c r="T71" s="55">
-        <v>671.85067064292286</v>
+        <v>668.46542609034987</v>
       </c>
       <c r="U71" s="55">
-        <v>677.30559892466749</v>
+        <v>673.85412155650181</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
@@ -32403,50 +32520,50 @@
         <v>0.08</v>
       </c>
       <c r="D72" s="56">
-        <v>532.62342976092805</v>
+        <v>529.99324439421787</v>
       </c>
       <c r="E72" s="56">
-        <v>540.87524516883343</v>
+        <v>538.13118769261052</v>
       </c>
       <c r="F72" s="56">
-        <v>550.33300924257617</v>
+        <v>547.45843799536897</v>
       </c>
       <c r="G72" s="56">
-        <v>561.3256170728389</v>
+        <v>558.29935175822948</v>
       </c>
       <c r="H72" s="56">
-        <v>574.31352178657801</v>
+        <v>571.10802801922262</v>
       </c>
       <c r="I72" s="56">
-        <v>589.96182234495222</v>
+        <v>586.54038761105926</v>
       </c>
       <c r="J72" s="56">
-        <v>609.26816718969962</v>
+        <v>605.58031178280578</v>
       </c>
       <c r="M72" s="83"/>
       <c r="N72" s="54">
         <v>0.08</v>
       </c>
       <c r="O72" s="56">
-        <v>524.42186221409941</v>
+        <v>521.90485555434077</v>
       </c>
       <c r="P72" s="56">
-        <v>534.97825544792329</v>
+        <v>532.31557432661145</v>
       </c>
       <c r="Q72" s="56">
-        <v>543.42337003498233</v>
+        <v>540.64414934442823</v>
       </c>
       <c r="R72" s="56">
-        <v>550.33300924257617</v>
+        <v>547.45843799536897</v>
       </c>
       <c r="S72" s="56">
-        <v>556.09104191557094</v>
+        <v>553.13701187115305</v>
       </c>
       <c r="T72" s="56">
-        <v>560.96322340810502</v>
+        <v>557.94195899681642</v>
       </c>
       <c r="U72" s="56">
-        <v>565.13937897313417</v>
+        <v>562.06048510452797</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
@@ -32455,50 +32572,50 @@
         <v>0.09</v>
       </c>
       <c r="D73" s="55">
-        <v>463.67739539194775</v>
+        <v>461.18646780678034</v>
       </c>
       <c r="E73" s="55">
-        <v>468.0060041623409</v>
+        <v>465.44824531380641</v>
       </c>
       <c r="F73" s="55">
-        <v>472.81952388440197</v>
+        <v>470.18744702254469</v>
       </c>
       <c r="G73" s="56">
-        <v>478.22985708543871</v>
+        <v>475.51424774877449</v>
       </c>
       <c r="H73" s="55">
-        <v>484.38620713519538</v>
+        <v>481.57554724686918</v>
       </c>
       <c r="I73" s="55">
-        <v>491.49203317423195</v>
+        <v>488.57166336370074</v>
       </c>
       <c r="J73" s="55">
-        <v>499.83217799933198</v>
+        <v>496.78304108489039</v>
       </c>
       <c r="M73" s="83"/>
       <c r="N73" s="54">
         <v>0.09</v>
       </c>
       <c r="O73" s="55">
-        <v>452.39987922242415</v>
+        <v>450.08307008806395</v>
       </c>
       <c r="P73" s="55">
-        <v>460.71899371434102</v>
+        <v>458.27374217248206</v>
       </c>
       <c r="Q73" s="55">
-        <v>467.37428530787457</v>
+        <v>464.82627984001647</v>
       </c>
       <c r="R73" s="56">
-        <v>472.81952388440197</v>
+        <v>470.18744702254469</v>
       </c>
       <c r="S73" s="55">
-        <v>477.35722269817478</v>
+        <v>474.65508634131811</v>
       </c>
       <c r="T73" s="55">
-        <v>481.19681400213648</v>
+        <v>478.43539653412648</v>
       </c>
       <c r="U73" s="55">
-        <v>484.48789226267502</v>
+        <v>481.67566241367649</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
@@ -32507,50 +32624,50 @@
         <v>0.1</v>
       </c>
       <c r="D74" s="55">
-        <v>409.84371514065094</v>
+        <v>407.46786485334604</v>
       </c>
       <c r="E74" s="55">
-        <v>411.93934116814791</v>
+        <v>409.52773623771355</v>
       </c>
       <c r="F74" s="55">
-        <v>414.18947045504473</v>
+        <v>411.73947481529854</v>
       </c>
       <c r="G74" s="56">
-        <v>416.62500365322143</v>
+        <v>414.13345402474431</v>
       </c>
       <c r="H74" s="55">
-        <v>419.2856701722381</v>
+        <v>416.74872543002135</v>
       </c>
       <c r="I74" s="55">
-        <v>422.2234238553653</v>
+        <v>419.63635646093672</v>
       </c>
       <c r="J74" s="55">
-        <v>425.50753649363077</v>
+        <v>422.86443702389988</v>
       </c>
       <c r="M74" s="83"/>
       <c r="N74" s="54">
         <v>0.1</v>
       </c>
       <c r="O74" s="55">
-        <v>397.74962136735172</v>
+        <v>395.58011515153896</v>
       </c>
       <c r="P74" s="55">
-        <v>404.4473376623377</v>
+        <v>402.1635579775151</v>
       </c>
       <c r="Q74" s="55">
-        <v>409.8055106983266</v>
+        <v>407.43031223829598</v>
       </c>
       <c r="R74" s="56">
-        <v>414.18947045504473</v>
+        <v>411.73947481529854</v>
       </c>
       <c r="S74" s="55">
-        <v>417.84277025230983</v>
+        <v>415.33044362946731</v>
       </c>
       <c r="T74" s="55">
-        <v>420.93402392691883</v>
+        <v>418.36895570299475</v>
       </c>
       <c r="U74" s="55">
-        <v>423.58366993372653</v>
+        <v>420.9733946231612</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
@@ -32559,50 +32676,50 @@
         <v>0.11</v>
       </c>
       <c r="D75" s="55">
-        <v>366.61218065049655</v>
+        <v>364.33488040104601</v>
       </c>
       <c r="E75" s="55">
-        <v>367.40370668821197</v>
+        <v>365.11163152471948</v>
       </c>
       <c r="F75" s="55">
-        <v>368.1952327259275</v>
+        <v>365.88838264839302</v>
       </c>
       <c r="G75" s="56">
-        <v>368.98675876364291</v>
+        <v>366.66513377206655</v>
       </c>
       <c r="H75" s="55">
-        <v>369.77828480135844</v>
+        <v>367.44188489574003</v>
       </c>
       <c r="I75" s="55">
-        <v>370.56981083907391</v>
+        <v>368.21863601941351</v>
       </c>
       <c r="J75" s="55">
-        <v>371.36133687678938</v>
+        <v>368.99538714308704</v>
       </c>
       <c r="M75" s="83"/>
       <c r="N75" s="54">
         <v>0.11</v>
       </c>
       <c r="O75" s="55">
-        <v>354.73929008476426</v>
+        <v>352.68361354594339</v>
       </c>
       <c r="P75" s="55">
-        <v>360.22134079042337</v>
+        <v>358.06333429138584</v>
       </c>
       <c r="Q75" s="55">
-        <v>364.60698135495068</v>
+        <v>362.36711088773978</v>
       </c>
       <c r="R75" s="56">
-        <v>368.1952327259275</v>
+        <v>365.88838264839302</v>
       </c>
       <c r="S75" s="55">
-        <v>371.18544220174152</v>
+        <v>368.8227757822707</v>
       </c>
       <c r="T75" s="55">
-        <v>373.71561945050723</v>
+        <v>371.30572381862873</v>
       </c>
       <c r="U75" s="55">
-        <v>375.8843428065922</v>
+        <v>373.43396499264998</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
@@ -32611,50 +32728,50 @@
         <v>0.12</v>
       </c>
       <c r="D76" s="55">
-        <v>331.11022800251112</v>
+        <v>328.91971877110495</v>
       </c>
       <c r="E76" s="55">
-        <v>331.13233050505312</v>
+        <v>328.94137360524792</v>
       </c>
       <c r="F76" s="55">
-        <v>331.08370499946068</v>
+        <v>328.89373297013339</v>
       </c>
       <c r="G76" s="56">
-        <v>330.95318390550193</v>
+        <v>328.7658554758786</v>
       </c>
       <c r="H76" s="55">
-        <v>330.72711795844918</v>
+        <v>328.54436831262694</v>
       </c>
       <c r="I76" s="55">
-        <v>330.38864630187425</v>
+        <v>328.21275212702596</v>
       </c>
       <c r="J76" s="55">
-        <v>329.91669286524149</v>
+        <v>327.75035772738511</v>
       </c>
       <c r="M76" s="84"/>
       <c r="N76" s="54">
         <v>0.12</v>
       </c>
       <c r="O76" s="55">
-        <v>319.92415146598933</v>
+        <v>317.96020721135289</v>
       </c>
       <c r="P76" s="55">
-        <v>324.47063623888505</v>
+        <v>322.41460659455976</v>
       </c>
       <c r="Q76" s="55">
-        <v>328.1078240572017</v>
+        <v>325.97812610112527</v>
       </c>
       <c r="R76" s="56">
-        <v>331.08370499946068</v>
+        <v>328.89373297013339</v>
       </c>
       <c r="S76" s="55">
-        <v>333.5636057846765</v>
+        <v>331.32340536097348</v>
       </c>
       <c r="T76" s="55">
-        <v>335.6619833721669</v>
+        <v>333.3792819993767</v>
       </c>
       <c r="U76" s="55">
-        <v>337.46059273287295</v>
+        <v>335.14146197515083</v>
       </c>
     </row>
   </sheetData>

--- a/MC.PA.xlsx
+++ b/MC.PA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470C30D9-A962-4C10-B48A-CA8E267EB484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEECF0B-50DA-477D-80AD-918E2EEB8463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{833B3248-1BC2-4BAF-AC24-6FD47873AD76}"/>
+    <workbookView xWindow="225" yWindow="1560" windowWidth="38175" windowHeight="15240" xr2:uid="{833B3248-1BC2-4BAF-AC24-6FD47873AD76}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="277">
   <si>
     <t>LVMH</t>
   </si>
@@ -979,6 +979,9 @@
   <si>
     <t>Q426</t>
   </si>
+  <si>
+    <t>Sale of Marc Jacob</t>
+  </si>
 </sst>
 </file>
 
@@ -995,13 +998,19 @@
     <numFmt numFmtId="171" formatCode="0.0"/>
     <numFmt numFmtId="172" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1334,147 +1343,148 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="14" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="8" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="15" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="9" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2077,7 +2087,7 @@
       <c r="I5" s="43">
         <v>497.68693999999999</v>
       </c>
-      <c r="J5" s="85" t="s">
+      <c r="J5" s="79" t="s">
         <v>272</v>
       </c>
     </row>
@@ -2110,7 +2120,7 @@
       <c r="I7" s="61">
         <v>8794</v>
       </c>
-      <c r="J7" s="85" t="s">
+      <c r="J7" s="79" t="s">
         <v>272</v>
       </c>
     </row>
@@ -2132,7 +2142,7 @@
         <f>12418+7925</f>
         <v>20343</v>
       </c>
-      <c r="J8" s="85" t="s">
+      <c r="J8" s="79" t="s">
         <v>272</v>
       </c>
     </row>
@@ -2259,6 +2269,9 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="58"/>
+      <c r="B18" s="87" t="s">
+        <v>276</v>
+      </c>
       <c r="H18" s="4" t="s">
         <v>256</v>
       </c>
@@ -2386,16 +2399,16 @@
       <c r="J2" s="57" t="s">
         <v>225</v>
       </c>
-      <c r="K2" s="85" t="s">
+      <c r="K2" s="79" t="s">
         <v>272</v>
       </c>
-      <c r="L2" s="85" t="s">
+      <c r="L2" s="79" t="s">
         <v>273</v>
       </c>
-      <c r="M2" s="85" t="s">
+      <c r="M2" s="79" t="s">
         <v>274</v>
       </c>
-      <c r="N2" s="85" t="s">
+      <c r="N2" s="79" t="s">
         <v>275</v>
       </c>
     </row>
@@ -2932,7 +2945,7 @@
         <f>+Model!Q19-SUM(Quarters!G15:I15)</f>
         <v>22715</v>
       </c>
-      <c r="K15" s="86">
+      <c r="K15" s="80">
         <v>19121</v>
       </c>
       <c r="L15" s="43"/>
@@ -30411,14 +30424,14 @@
       </c>
       <c r="E4" s="7">
         <f ca="1">+TODAY()</f>
-        <v>46129</v>
+        <v>46157</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>158</v>
       </c>
       <c r="J4" s="8">
         <f ca="1">V62</f>
-        <v>470.18744702254469</v>
+        <v>469.04213348610131</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>159</v>
@@ -30440,7 +30453,7 @@
       </c>
       <c r="J5" s="11">
         <f ca="1">J4/J3-1</f>
-        <v>-5.830673538444886E-2</v>
+        <v>-6.060057383116102E-2</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>161</v>
@@ -32038,43 +32051,43 @@
       <c r="L52" s="40"/>
       <c r="M52" s="40">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>4117.8650809753517</v>
+        <v>5160.7301896147474</v>
       </c>
       <c r="N52" s="40">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>13637.780229757209</v>
+        <v>13546.675812134705</v>
       </c>
       <c r="O52" s="40">
         <f t="shared" ref="O52:U52" ca="1" si="20">O51/(1+$E$18)^O53</f>
-        <v>14010.3045573772</v>
+        <v>13916.71156673575</v>
       </c>
       <c r="P52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>14337.300947776755</v>
+        <v>14241.523524242995</v>
       </c>
       <c r="Q52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>14688.818326116987</v>
+        <v>14590.692662217249</v>
       </c>
       <c r="R52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>14993.963811463174</v>
+        <v>14893.799685199014</v>
       </c>
       <c r="S52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>14117.943993949606</v>
+        <v>14023.631939940298</v>
       </c>
       <c r="T52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>12929.702607992975</v>
+        <v>12843.328358937168</v>
       </c>
       <c r="U52" s="40">
         <f t="shared" ca="1" si="20"/>
-        <v>11832.783337185789</v>
+        <v>11753.736834263313</v>
       </c>
       <c r="V52" s="41">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>10820.458796927922</v>
+        <v>10748.174922243428</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -32083,43 +32096,43 @@
       </c>
       <c r="M53" s="42">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.29722222222222222</v>
+        <v>0.375</v>
       </c>
       <c r="N53" s="42">
         <f ca="1">M53+1</f>
-        <v>1.2972222222222223</v>
+        <v>1.375</v>
       </c>
       <c r="O53" s="42">
         <f ca="1">N53+1</f>
-        <v>2.2972222222222225</v>
+        <v>2.375</v>
       </c>
       <c r="P53" s="42">
         <f t="shared" ref="P53:V53" ca="1" si="21">O53+1</f>
-        <v>3.2972222222222225</v>
+        <v>3.375</v>
       </c>
       <c r="Q53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>4.2972222222222225</v>
+        <v>4.375</v>
       </c>
       <c r="R53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>5.2972222222222225</v>
+        <v>5.375</v>
       </c>
       <c r="S53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>6.2972222222222225</v>
+        <v>6.375</v>
       </c>
       <c r="T53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>7.2972222222222225</v>
+        <v>7.375</v>
       </c>
       <c r="U53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>8.2972222222222225</v>
+        <v>8.375</v>
       </c>
       <c r="V53" s="42">
         <f t="shared" ca="1" si="21"/>
-        <v>9.2972222222222225</v>
+        <v>9.375</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -32132,7 +32145,7 @@
       <c r="Q54" s="43"/>
       <c r="V54" s="21">
         <f ca="1">SUM(M52:V52)</f>
-        <v>125486.92168952296</v>
+        <v>125719.00549552868</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -32176,7 +32189,7 @@
       <c r="U56" s="45"/>
       <c r="V56" s="46">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>120068.23004553939</v>
+        <v>119266.13865024062</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -32204,7 +32217,7 @@
       <c r="U57" s="48"/>
       <c r="V57" s="49">
         <f ca="1">V54+V56</f>
-        <v>245555.15173506236</v>
+        <v>244985.1441457693</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -32258,7 +32271,7 @@
       <c r="Q60" s="43"/>
       <c r="V60" s="50">
         <f ca="1">V57+V58-V59</f>
-        <v>234006.15173506236</v>
+        <v>233436.1441457693</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -32295,7 +32308,7 @@
       </c>
       <c r="V62" s="50">
         <f ca="1">V60/V61</f>
-        <v>470.18744702254469</v>
+        <v>469.04213348610131</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
@@ -32328,35 +32341,35 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B68" s="51"/>
-      <c r="C68" s="79" t="s">
+      <c r="C68" s="81" t="s">
         <v>174</v>
       </c>
-      <c r="D68" s="79"/>
-      <c r="E68" s="79"/>
-      <c r="F68" s="79"/>
-      <c r="G68" s="79"/>
-      <c r="H68" s="79"/>
-      <c r="I68" s="79"/>
-      <c r="J68" s="80"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
+      <c r="H68" s="81"/>
+      <c r="I68" s="81"/>
+      <c r="J68" s="82"/>
       <c r="M68" s="51"/>
-      <c r="N68" s="81" t="s">
+      <c r="N68" s="83" t="s">
         <v>201</v>
       </c>
-      <c r="O68" s="81"/>
-      <c r="P68" s="81"/>
-      <c r="Q68" s="81"/>
-      <c r="R68" s="81"/>
-      <c r="S68" s="81"/>
-      <c r="T68" s="81"/>
-      <c r="U68" s="82"/>
+      <c r="O68" s="83"/>
+      <c r="P68" s="83"/>
+      <c r="Q68" s="83"/>
+      <c r="R68" s="83"/>
+      <c r="S68" s="83"/>
+      <c r="T68" s="83"/>
+      <c r="U68" s="84"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B69" s="83" t="s">
+      <c r="B69" s="85" t="s">
         <v>172</v>
       </c>
       <c r="C69" s="52">
         <f ca="1">+J4</f>
-        <v>470.18744702254469</v>
+        <v>469.04213348610131</v>
       </c>
       <c r="D69" s="53">
         <v>0.01</v>
@@ -32379,12 +32392,12 @@
       <c r="J69" s="53">
         <v>0.04</v>
       </c>
-      <c r="M69" s="83" t="s">
+      <c r="M69" s="85" t="s">
         <v>172</v>
       </c>
       <c r="N69" s="52">
         <f ca="1">+J4</f>
-        <v>470.18744702254469</v>
+        <v>469.04213348610131</v>
       </c>
       <c r="O69" s="53">
         <v>0.08</v>
@@ -32409,369 +32422,369 @@
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B70" s="83"/>
+      <c r="B70" s="85"/>
       <c r="C70" s="54">
         <v>0.06</v>
       </c>
       <c r="D70" s="55">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>748.85927750064809</v>
+        <v>747.54150091051793</v>
       </c>
       <c r="E70" s="55">
-        <v>778.13685957382859</v>
+        <v>776.68669643129317</v>
       </c>
       <c r="F70" s="55">
-        <v>814.43576223469506</v>
+        <v>812.82146372854402</v>
       </c>
       <c r="G70" s="56">
-        <v>860.76512287796993</v>
+        <v>858.94133356361669</v>
       </c>
       <c r="H70" s="55">
-        <v>922.14017049485699</v>
+        <v>920.03885720542269</v>
       </c>
       <c r="I70" s="55">
-        <v>1007.5883172695244</v>
+        <v>1005.1006269380021</v>
       </c>
       <c r="J70" s="55">
-        <v>1135.1643875703071</v>
-      </c>
-      <c r="M70" s="83"/>
+        <v>1132.0998273294342</v>
+      </c>
+      <c r="M70" s="85"/>
       <c r="N70" s="54">
         <v>0.06</v>
       </c>
       <c r="O70" s="55">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>768.83029785147153</v>
+        <v>767.4222168596441</v>
       </c>
       <c r="P70" s="55">
-        <v>787.41030185945147</v>
+        <v>785.9182063247514</v>
       </c>
       <c r="Q70" s="55">
-        <v>802.27430506583562</v>
+        <v>800.7149978968373</v>
       </c>
       <c r="R70" s="56">
-        <v>814.43576223469506</v>
+        <v>812.82146372854402</v>
       </c>
       <c r="S70" s="55">
-        <v>824.57030987541134</v>
+        <v>822.910185254966</v>
       </c>
       <c r="T70" s="55">
-        <v>833.14569634063309</v>
+        <v>831.44679577732336</v>
       </c>
       <c r="U70" s="55">
-        <v>840.49602759653726</v>
+        <v>838.76389051077251</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="83"/>
+      <c r="B71" s="85"/>
       <c r="C71" s="54">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="55">
-        <v>621.38718260457085</v>
+        <v>620.16971195178076</v>
       </c>
       <c r="E71" s="55">
-        <v>636.65085971663677</v>
+        <v>635.35327738780859</v>
       </c>
       <c r="F71" s="55">
-        <v>654.7487467219629</v>
+        <v>653.35617731694697</v>
       </c>
       <c r="G71" s="56">
-        <v>676.6255802516356</v>
+        <v>675.11818990356619</v>
       </c>
       <c r="H71" s="55">
-        <v>703.69846525228479</v>
+        <v>702.04898239422153</v>
       </c>
       <c r="I71" s="55">
-        <v>738.19428092575811</v>
+        <v>736.36374617635704</v>
       </c>
       <c r="J71" s="55">
-        <v>783.82449260846681</v>
-      </c>
-      <c r="M71" s="83"/>
+        <v>781.75446689571265</v>
+      </c>
+      <c r="M71" s="85"/>
       <c r="N71" s="54">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="55">
-        <v>621.3143407615197</v>
+        <v>620.09725242041577</v>
       </c>
       <c r="P71" s="55">
-        <v>634.93576541207062</v>
+        <v>633.64718478566931</v>
       </c>
       <c r="Q71" s="55">
-        <v>645.83290513251143</v>
+        <v>644.48713067787207</v>
       </c>
       <c r="R71" s="56">
-        <v>654.7487467219629</v>
+        <v>653.35617731694697</v>
       </c>
       <c r="S71" s="55">
-        <v>662.17861471317246</v>
+        <v>660.74704951617628</v>
       </c>
       <c r="T71" s="55">
-        <v>668.46542609034987</v>
+        <v>667.00086445398551</v>
       </c>
       <c r="U71" s="55">
-        <v>673.85412155650181</v>
+        <v>672.36127725782217</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="83"/>
+      <c r="B72" s="85"/>
       <c r="C72" s="54">
         <v>0.08</v>
       </c>
       <c r="D72" s="56">
-        <v>529.99324439421787</v>
+        <v>528.84990960345237</v>
       </c>
       <c r="E72" s="56">
-        <v>538.13118769261052</v>
+        <v>536.93928582554884</v>
       </c>
       <c r="F72" s="56">
-        <v>547.45843799536897</v>
+        <v>546.21087129255261</v>
       </c>
       <c r="G72" s="56">
-        <v>558.29935175822948</v>
+        <v>556.98708670762005</v>
       </c>
       <c r="H72" s="56">
-        <v>571.10802801922262</v>
+        <v>569.7193210551701</v>
       </c>
       <c r="I72" s="56">
-        <v>586.54038761105926</v>
+        <v>585.05958064603067</v>
       </c>
       <c r="J72" s="56">
-        <v>605.58031178280578</v>
-      </c>
-      <c r="M72" s="83"/>
+        <v>603.98587494644323</v>
+      </c>
+      <c r="M72" s="85"/>
       <c r="N72" s="54">
         <v>0.08</v>
       </c>
       <c r="O72" s="56">
-        <v>521.90485555434077</v>
+        <v>520.8097920998938</v>
       </c>
       <c r="P72" s="56">
-        <v>532.31557432661145</v>
+        <v>531.1583799191252</v>
       </c>
       <c r="Q72" s="56">
-        <v>540.64414934442823</v>
+        <v>539.43725017451027</v>
       </c>
       <c r="R72" s="56">
-        <v>547.45843799536897</v>
+        <v>546.21087129255261</v>
       </c>
       <c r="S72" s="56">
-        <v>553.13701187115305</v>
+        <v>551.85555555758788</v>
       </c>
       <c r="T72" s="56">
-        <v>557.94195899681642</v>
+        <v>556.63182685877166</v>
       </c>
       <c r="U72" s="56">
-        <v>562.06048510452797</v>
+        <v>560.72577368835766</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="83"/>
+      <c r="B73" s="85"/>
       <c r="C73" s="54">
         <v>0.09</v>
       </c>
       <c r="D73" s="55">
-        <v>461.18646780678034</v>
+        <v>460.10128348166535</v>
       </c>
       <c r="E73" s="55">
-        <v>465.44824531380641</v>
+        <v>464.33459105067567</v>
       </c>
       <c r="F73" s="55">
-        <v>470.18744702254469</v>
+        <v>469.04213348610131</v>
       </c>
       <c r="G73" s="56">
-        <v>475.51424774877449</v>
+        <v>474.3333496032688</v>
       </c>
       <c r="H73" s="55">
-        <v>481.57554724686918</v>
+        <v>480.35415782261384</v>
       </c>
       <c r="I73" s="55">
-        <v>488.57166336370074</v>
+        <v>487.30353780836651</v>
       </c>
       <c r="J73" s="55">
-        <v>496.78304108489039</v>
-      </c>
-      <c r="M73" s="83"/>
+        <v>495.46006109044913</v>
+      </c>
+      <c r="M73" s="85"/>
       <c r="N73" s="54">
         <v>0.09</v>
       </c>
       <c r="O73" s="55">
-        <v>450.08307008806395</v>
+        <v>449.07205975356561</v>
       </c>
       <c r="P73" s="55">
-        <v>458.27374217248206</v>
+        <v>457.20801571867275</v>
       </c>
       <c r="Q73" s="55">
-        <v>464.82627984001647</v>
+        <v>463.71678049075848</v>
       </c>
       <c r="R73" s="56">
-        <v>470.18744702254469</v>
+        <v>469.04213348610131</v>
       </c>
       <c r="S73" s="55">
-        <v>474.65508634131811</v>
+        <v>473.47992764888699</v>
       </c>
       <c r="T73" s="55">
-        <v>478.43539653412648</v>
+        <v>477.23498424816722</v>
       </c>
       <c r="U73" s="55">
-        <v>481.67566241367649</v>
+        <v>480.45360419040742</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="83"/>
+      <c r="B74" s="85"/>
       <c r="C74" s="54">
         <v>0.1</v>
       </c>
       <c r="D74" s="55">
-        <v>407.46786485334604</v>
+        <v>406.43042630749142</v>
       </c>
       <c r="E74" s="55">
-        <v>409.52773623771355</v>
+        <v>408.47508429471077</v>
       </c>
       <c r="F74" s="55">
-        <v>411.73947481529854</v>
+        <v>410.6704878439906</v>
       </c>
       <c r="G74" s="56">
-        <v>414.13345402474431</v>
+        <v>413.0467860677428</v>
       </c>
       <c r="H74" s="55">
-        <v>416.74872543002135</v>
+        <v>415.64274211049741</v>
       </c>
       <c r="I74" s="55">
-        <v>419.63635646093672</v>
+        <v>418.50904623817792</v>
       </c>
       <c r="J74" s="55">
-        <v>422.86443702389988</v>
-      </c>
-      <c r="M74" s="83"/>
+        <v>421.71328547201585</v>
+      </c>
+      <c r="M74" s="85"/>
       <c r="N74" s="54">
         <v>0.1</v>
       </c>
       <c r="O74" s="55">
-        <v>395.58011515153896</v>
+        <v>394.63047483366267</v>
       </c>
       <c r="P74" s="55">
-        <v>402.1635579775151</v>
+        <v>401.16529494898151</v>
       </c>
       <c r="Q74" s="55">
-        <v>407.43031223829598</v>
+        <v>406.39315104123648</v>
       </c>
       <c r="R74" s="56">
-        <v>411.73947481529854</v>
+        <v>410.6704878439906</v>
       </c>
       <c r="S74" s="55">
-        <v>415.33044362946731</v>
+        <v>414.23493517961896</v>
       </c>
       <c r="T74" s="55">
-        <v>418.36895570299475</v>
+        <v>417.25100600207384</v>
       </c>
       <c r="U74" s="55">
-        <v>420.9733946231612</v>
+        <v>419.83620956417798</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="83"/>
+      <c r="B75" s="85"/>
       <c r="C75" s="54">
         <v>0.11</v>
       </c>
       <c r="D75" s="55">
-        <v>364.33488040104601</v>
+        <v>363.33807315729501</v>
       </c>
       <c r="E75" s="55">
-        <v>365.11163152471948</v>
+        <v>364.10854499608536</v>
       </c>
       <c r="F75" s="55">
-        <v>365.88838264839302</v>
+        <v>364.87901683487581</v>
       </c>
       <c r="G75" s="56">
-        <v>366.66513377206655</v>
+        <v>365.64948867366627</v>
       </c>
       <c r="H75" s="55">
-        <v>367.44188489574003</v>
+        <v>366.41996051245667</v>
       </c>
       <c r="I75" s="55">
-        <v>368.21863601941351</v>
+        <v>367.19043235124707</v>
       </c>
       <c r="J75" s="55">
-        <v>368.99538714308704</v>
-      </c>
-      <c r="M75" s="83"/>
+        <v>367.96090419003741</v>
+      </c>
+      <c r="M75" s="85"/>
       <c r="N75" s="54">
         <v>0.11</v>
       </c>
       <c r="O75" s="55">
-        <v>352.68361354594339</v>
+        <v>351.78099557543896</v>
       </c>
       <c r="P75" s="55">
-        <v>358.06333429138584</v>
+        <v>357.11722645891331</v>
       </c>
       <c r="Q75" s="55">
-        <v>362.36711088773978</v>
+        <v>361.38621116569271</v>
       </c>
       <c r="R75" s="56">
-        <v>365.88838264839302</v>
+        <v>364.87901683487581</v>
       </c>
       <c r="S75" s="55">
-        <v>368.8227757822707</v>
+        <v>367.78968822586182</v>
       </c>
       <c r="T75" s="55">
-        <v>371.30572381862873</v>
+        <v>370.25256401823452</v>
       </c>
       <c r="U75" s="55">
-        <v>373.43396499264998</v>
+        <v>372.36360041169695</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="84"/>
+      <c r="B76" s="86"/>
       <c r="C76" s="54">
         <v>0.12</v>
       </c>
       <c r="D76" s="55">
-        <v>328.91971877110495</v>
+        <v>327.95847803204038</v>
       </c>
       <c r="E76" s="55">
-        <v>328.94137360524792</v>
+        <v>327.97994282942449</v>
       </c>
       <c r="F76" s="55">
-        <v>328.89373297013339</v>
+        <v>327.93272027517941</v>
       </c>
       <c r="G76" s="56">
-        <v>328.7658554758786</v>
+        <v>327.80596499799532</v>
       </c>
       <c r="H76" s="55">
-        <v>328.54436831262694</v>
+        <v>327.58642154404896</v>
       </c>
       <c r="I76" s="55">
-        <v>328.21275212702596</v>
+        <v>327.25771552920583</v>
       </c>
       <c r="J76" s="55">
-        <v>327.75035772738511</v>
-      </c>
-      <c r="M76" s="84"/>
+        <v>326.79937897329785</v>
+      </c>
+      <c r="M76" s="86"/>
       <c r="N76" s="54">
         <v>0.12</v>
       </c>
       <c r="O76" s="55">
-        <v>317.96020721135289</v>
+        <v>317.0951440759369</v>
       </c>
       <c r="P76" s="55">
-        <v>322.41460659455976</v>
+        <v>321.51045289785048</v>
       </c>
       <c r="Q76" s="55">
-        <v>325.97812610112527</v>
+        <v>325.04269995538141</v>
       </c>
       <c r="R76" s="56">
-        <v>328.89373297013339</v>
+        <v>327.93272027517941</v>
       </c>
       <c r="S76" s="55">
-        <v>331.32340536097348</v>
+        <v>330.34107054167777</v>
       </c>
       <c r="T76" s="55">
-        <v>333.3792819993767</v>
+        <v>332.37890538256102</v>
       </c>
       <c r="U76" s="55">
-        <v>335.14146197515083</v>
+        <v>334.12562096046088</v>
       </c>
     </row>
   </sheetData>
